--- a/output/pdf_financials_xlsx/CSU.xlsx
+++ b/output/pdf_financials_xlsx/CSU.xlsx
@@ -2462,13 +2462,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>8.395</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>19.606</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>22.052</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>110.73</v>
@@ -2501,20 +2501,14 @@
           <t xml:space="preserve">  Total Current Assets</t>
         </is>
       </c>
-      <c r="B49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B49" s="3" t="n">
+        <v>8.395</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>19.606</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>22.052</v>
       </c>
       <c r="E49" s="3" t="n">
         <v>220.528</v>
@@ -12467,7 +12461,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -14009,7 +14003,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">

--- a/output/pdf_financials_xlsx/CSU.xlsx
+++ b/output/pdf_financials_xlsx/CSU.xlsx
@@ -1902,31 +1902,31 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>30.405</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>33.249</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>30.911</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>33.492</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>41.313</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>77.967</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>763</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>811</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1284</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>1980</v>
@@ -1982,31 +1982,31 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>30.405</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>33.249</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>30.911</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>33.492</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>41.313</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>77.967</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>763</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>811</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1284</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>1980</v>
@@ -2471,22 +2471,22 @@
         <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>110.73</v>
+        <v>77.238</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>107.887</v>
+        <v>66.574</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>199.59</v>
+        <v>121.623</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1200</v>
+        <v>437</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1526</v>
+        <v>715</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>2150</v>
+        <v>866</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>964</v>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E44" s="5" t="n">

--- a/output/pdf_financials_xlsx/CSU.xlsx
+++ b/output/pdf_financials_xlsx/CSU.xlsx
@@ -1680,28 +1680,28 @@
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>84.518</v>
+        <v>76.65000000000001</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>92.785</v>
+        <v>85.142</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>129.088</v>
+        <v>119.144</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>639</v>
+        <v>518</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>819</v>
+        <v>676</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>1021</v>
+        <v>859</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>1226</v>
+        <v>1044</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>1383</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="29">
@@ -1726,28 +1726,28 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>173.756</v>
+        <v>165.888</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>226.645</v>
+        <v>219.002</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>248.379</v>
+        <v>238.435</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>1013</v>
+        <v>892</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1544</v>
+        <v>1401</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>1286</v>
+        <v>1124</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>2237</v>
+        <v>2055</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>2322</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="30">
@@ -1772,28 +1772,28 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>22.46822553052276</v>
+        <v>21.45082182374916</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>25.43069883508785</v>
+        <v>24.57311613440362</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>20.51403397490535</v>
+        <v>19.69274250563275</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>19.83940462201332</v>
+        <v>17.46964355660008</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>23.31621866505587</v>
+        <v>21.15675022651767</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>15.29677649577733</v>
+        <v>13.36981087189247</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>22.22332604808265</v>
+        <v>20.41525928869461</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>19.97763056009636</v>
+        <v>18.2483007829304</v>
       </c>
     </row>
     <row r="31">
@@ -4604,28 +4604,28 @@
         </is>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>76.65000000000001</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>85.142</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>119.144</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>518</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>676</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>859</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>1044</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="101">
@@ -5828,10 +5828,10 @@
         <v>0</v>
       </c>
       <c r="K126" s="3" t="n">
-        <v>0</v>
+        <v>-89</v>
       </c>
       <c r="L126" s="3" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="127">
@@ -14354,7 +14354,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -15800,7 +15800,11 @@
           <t>Dividends paid to non-controlling interests</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
           <t>-</t>
@@ -17264,7 +17268,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -17883,7 +17887,11 @@
           <t>Dividends paid to non-controlling interests (note 28)</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
           <t>-</t>
@@ -18770,7 +18778,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -22641,7 +22649,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -23993,7 +24001,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
